--- a/data/trans_dic/P34B03_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,87; 31,89</t>
+          <t>23,77; 32,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,18; 39,57</t>
+          <t>29,72; 39,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,72; 45,67</t>
+          <t>28,59; 45,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 13,93</t>
+          <t>8,05; 13,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 20,68</t>
+          <t>13,52; 21,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,47; 22,6</t>
+          <t>11,77; 23,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,95</t>
+          <t>17,0; 22,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,41; 29,19</t>
+          <t>23,44; 29,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,45; 33,38</t>
+          <t>23,05; 33,42</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,46; 30,6</t>
+          <t>23,53; 30,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,64; 31,14</t>
+          <t>23,89; 31,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,98; 34,53</t>
+          <t>22,73; 34,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,46</t>
+          <t>8,17; 13,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 17,51</t>
+          <t>11,6; 17,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,6</t>
+          <t>6,74; 14,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,07; 21,67</t>
+          <t>17,23; 21,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 23,19</t>
+          <t>18,68; 23,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,01; 22,42</t>
+          <t>14,35; 22,44</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,21</t>
+          <t>13,19; 19,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,78; 21,8</t>
+          <t>15,95; 21,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 24,7</t>
+          <t>17,27; 24,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,2</t>
+          <t>5,97; 10,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,89; 15,14</t>
+          <t>10,1; 15,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 12,71</t>
+          <t>8,45; 13,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,86</t>
+          <t>10,14; 13,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 17,56</t>
+          <t>13,61; 17,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,49; 17,67</t>
+          <t>13,52; 17,85</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,38</t>
+          <t>9,0; 14,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,2</t>
+          <t>9,76; 15,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,05</t>
+          <t>5,28; 18,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,8</t>
+          <t>3,81; 7,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 11,74</t>
+          <t>7,0; 11,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 10,6</t>
+          <t>7,03; 10,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,2</t>
+          <t>6,8; 10,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 12,69</t>
+          <t>9,28; 13,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,51</t>
+          <t>6,86; 13,57</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,81</t>
+          <t>2,98; 7,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,27</t>
+          <t>4,96; 9,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 10,69</t>
+          <t>6,39; 10,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,52</t>
+          <t>2,42; 6,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,29</t>
+          <t>3,13; 7,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,58</t>
+          <t>5,4; 8,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,34</t>
+          <t>3,33; 6,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,71</t>
+          <t>4,44; 7,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,14</t>
+          <t>6,28; 9,23</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,02</t>
+          <t>2,06; 7,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,84</t>
+          <t>2,88; 7,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,58</t>
+          <t>5,41; 9,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,95</t>
+          <t>1,03; 4,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,8</t>
+          <t>3,04; 7,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,05</t>
+          <t>1,2; 5,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,57</t>
+          <t>2,03; 5,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,73</t>
+          <t>3,54; 6,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,29</t>
+          <t>2,11; 6,24</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,53</t>
+          <t>1,22; 7,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,13</t>
+          <t>0,94; 4,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,36</t>
+          <t>2,45; 6,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,93</t>
+          <t>0,56; 3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,29</t>
+          <t>0,34; 3,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,91</t>
+          <t>0,78; 3,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,74</t>
+          <t>1,06; 3,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,87</t>
+          <t>0,94; 2,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,63</t>
+          <t>1,65; 3,5</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 16,95</t>
+          <t>14,27; 16,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,63; 18,2</t>
+          <t>15,51; 18,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,25; 18,7</t>
+          <t>12,87; 18,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,56</t>
+          <t>5,77; 7,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,5</t>
+          <t>8,51; 10,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,03</t>
+          <t>6,4; 8,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,78</t>
+          <t>10,21; 11,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,31; 13,96</t>
+          <t>12,27; 13,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,27</t>
+          <t>10,5; 13,31</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic,correr, natación, 3 veces por semana o más</t>
+          <t>Población que realiza alguna actividad física moderada, como montar en bicicleta, gimnasia, aeróbic, correr, natación, durante más de 30 minutos, 3 veces por semana o más (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108124; 144432</t>
+          <t>107655; 145407</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>126609; 165975</t>
+          <t>124665; 165278</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110867; 182693</t>
+          <t>114374; 180001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35846; 59938</t>
+          <t>34645; 58867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52032; 81841</t>
+          <t>53522; 83353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35751; 70430</t>
+          <t>36669; 73735</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>151628; 202732</t>
+          <t>150104; 199411</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>190855; 237980</t>
+          <t>191123; 240589</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>159740; 237494</t>
+          <t>164019; 237822</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>160946; 209995</t>
+          <t>161440; 211080</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139620; 183890</t>
+          <t>141069; 184238</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97326; 146250</t>
+          <t>96265; 146500</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50436; 82169</t>
+          <t>49866; 82623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66132; 98682</t>
+          <t>65345; 97835</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35466; 74689</t>
+          <t>34487; 75470</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>221291; 280930</t>
+          <t>223345; 279527</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>216369; 267626</t>
+          <t>215592; 271406</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131005; 209672</t>
+          <t>134201; 209838</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89961; 131014</t>
+          <t>89969; 130530</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>105572; 145839</t>
+          <t>106740; 146578</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93099; 132456</t>
+          <t>92577; 129962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42562; 72348</t>
+          <t>42333; 73075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>65425; 100110</t>
+          <t>66814; 99537</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45778; 68860</t>
+          <t>45790; 70554</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>141155; 192773</t>
+          <t>141042; 192881</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>180949; 233589</t>
+          <t>181075; 236082</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145405; 190507</t>
+          <t>145712; 192446</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55019; 88381</t>
+          <t>55295; 88763</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63799; 98200</t>
+          <t>63054; 100216</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50215; 160251</t>
+          <t>46837; 162806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23745; 48080</t>
+          <t>23499; 47311</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45761; 76212</t>
+          <t>45448; 76377</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49664; 75490</t>
+          <t>50063; 76348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84390; 125500</t>
+          <t>83737; 125676</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117922; 164292</t>
+          <t>120161; 168349</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>107296; 216123</t>
+          <t>109820; 217133</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13729; 33559</t>
+          <t>12818; 33077</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22299; 44289</t>
+          <t>23727; 46407</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35174; 59901</t>
+          <t>35776; 60026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11619; 29212</t>
+          <t>10818; 30540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15178; 36208</t>
+          <t>15531; 36112</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29396; 46826</t>
+          <t>29462; 47965</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29153; 55628</t>
+          <t>29184; 55352</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43481; 75160</t>
+          <t>43265; 75261</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>70762; 101016</t>
+          <t>69467; 102029</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6371; 24854</t>
+          <t>6393; 24568</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9290; 26198</t>
+          <t>9632; 26611</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19216; 35181</t>
+          <t>19870; 35689</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3762; 17521</t>
+          <t>3656; 17114</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11674; 29477</t>
+          <t>11465; 28702</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6076; 30743</t>
+          <t>7327; 31933</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13129; 36975</t>
+          <t>13482; 36314</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24352; 47957</t>
+          <t>25209; 48354</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21559; 61337</t>
+          <t>20605; 60846</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2209; 16308</t>
+          <t>3045; 18955</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2418; 10603</t>
+          <t>2412; 11279</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6647; 17975</t>
+          <t>6925; 17641</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2104; 11416</t>
+          <t>2176; 12467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1333; 13172</t>
+          <t>1362; 13194</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3227; 12392</t>
+          <t>3309; 13174</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7410; 23873</t>
+          <t>6777; 24470</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5333; 18891</t>
+          <t>6202; 19267</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11259; 25702</t>
+          <t>11705; 24770</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>491617; 580500</t>
+          <t>488666; 574007</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>530515; 617833</t>
+          <t>526414; 614737</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>458096; 646747</t>
+          <t>445002; 644667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>204231; 268913</t>
+          <t>205139; 265688</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>299589; 372128</t>
+          <t>301638; 373426</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>231399; 330164</t>
+          <t>234173; 327856</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>716225; 822701</t>
+          <t>712616; 823438</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>854371; 968685</t>
+          <t>851221; 963781</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>747120; 943736</t>
+          <t>746871; 946601</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P34B03_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P34B03_R-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,77; 32,1</t>
+          <t>23,98; 32,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,72; 39,4</t>
+          <t>30,6; 40,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,59; 45,0</t>
+          <t>27,23; 41,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 13,68</t>
+          <t>7,99; 14,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 21,06</t>
+          <t>13,49; 21,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,77; 23,66</t>
+          <t>11,31; 21,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,0; 22,58</t>
+          <t>17,07; 22,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,44; 29,51</t>
+          <t>22,88; 28,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,05; 33,42</t>
+          <t>21,3; 31,29</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,53; 30,76</t>
+          <t>23,26; 30,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,89; 31,2</t>
+          <t>23,97; 31,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 34,59</t>
+          <t>22,92; 33,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 13,54</t>
+          <t>8,18; 13,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 17,36</t>
+          <t>11,59; 17,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 14,75</t>
+          <t>8,81; 15,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 21,56</t>
+          <t>17,11; 21,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 23,52</t>
+          <t>18,71; 23,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 22,44</t>
+          <t>16,71; 23,19</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,14</t>
+          <t>13,36; 19,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,95; 21,91</t>
+          <t>16,19; 22,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,27; 24,24</t>
+          <t>16,99; 24,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,31</t>
+          <t>5,87; 10,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 15,05</t>
+          <t>9,92; 15,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,02</t>
+          <t>8,35; 12,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 13,87</t>
+          <t>10,19; 13,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,61; 17,74</t>
+          <t>13,66; 17,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 17,85</t>
+          <t>13,4; 17,52</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 14,44</t>
+          <t>9,17; 14,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,51</t>
+          <t>10,26; 15,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 18,34</t>
+          <t>14,11; 20,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,68</t>
+          <t>3,8; 7,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,77</t>
+          <t>7,08; 11,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 10,72</t>
+          <t>7,85; 11,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,21</t>
+          <t>6,94; 10,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 13,0</t>
+          <t>9,2; 12,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 13,57</t>
+          <t>11,48; 14,76</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,7</t>
+          <t>3,22; 7,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,71</t>
+          <t>4,83; 9,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,39; 10,71</t>
+          <t>6,92; 11,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,82</t>
+          <t>2,55; 6,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,27</t>
+          <t>3,16; 7,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,79</t>
+          <t>5,4; 8,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 6,31</t>
+          <t>3,22; 6,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,72</t>
+          <t>4,51; 7,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,23</t>
+          <t>6,72; 9,56</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,93</t>
+          <t>2,06; 8,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,96</t>
+          <t>2,66; 7,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,41; 9,71</t>
+          <t>5,29; 10,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,83</t>
+          <t>1,06; 4,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,6</t>
+          <t>2,95; 7,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,25</t>
+          <t>3,56; 6,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,47</t>
+          <t>1,78; 5,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,79</t>
+          <t>3,29; 6,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,24</t>
+          <t>4,9; 7,71</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 7,59</t>
+          <t>0,88; 6,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,39</t>
+          <t>0,93; 4,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,24</t>
+          <t>2,63; 6,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,2</t>
+          <t>0,55; 3,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,3</t>
+          <t>0,34; 3,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,1</t>
+          <t>0,77; 2,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,83</t>
+          <t>1,01; 3,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,93</t>
+          <t>0,81; 2,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,5</t>
+          <t>1,76; 3,83</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 16,76</t>
+          <t>14,36; 16,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,51; 18,11</t>
+          <t>15,55; 18,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,87; 18,64</t>
+          <t>15,85; 19,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,47</t>
+          <t>5,74; 7,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,54</t>
+          <t>8,56; 10,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,97</t>
+          <t>7,82; 9,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,21; 11,8</t>
+          <t>10,22; 11,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,27; 13,89</t>
+          <t>12,21; 13,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,31</t>
+          <t>12,06; 13,81</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144805</t>
+          <t>141428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>57706</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>196842</t>
+          <t>199133</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107655; 145407</t>
+          <t>108612; 145338</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124665; 165278</t>
+          <t>128356; 168327</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>114374; 180001</t>
+          <t>111031; 171071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34645; 58867</t>
+          <t>34364; 61007</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53522; 83353</t>
+          <t>53373; 83532</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36669; 73735</t>
+          <t>40781; 78481</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>150104; 199411</t>
+          <t>150777; 196197</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>191123; 240589</t>
+          <t>186558; 235920</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>164019; 237822</t>
+          <t>163644; 240378</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120081</t>
+          <t>133236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55164</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>175245</t>
+          <t>192706</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>161440; 211080</t>
+          <t>159622; 208528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141069; 184238</t>
+          <t>141518; 187529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96265; 146500</t>
+          <t>109322; 160677</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49866; 82623</t>
+          <t>49929; 81338</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65345; 97835</t>
+          <t>65290; 96710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34487; 75470</t>
+          <t>44156; 77319</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>223345; 279527</t>
+          <t>221784; 277347</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>215592; 271406</t>
+          <t>215948; 270573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>134201; 209838</t>
+          <t>163418; 226749</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110339</t>
+          <t>125948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56870</t>
+          <t>64633</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167209</t>
+          <t>190581</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89969; 130530</t>
+          <t>91101; 131352</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>106740; 146578</t>
+          <t>108312; 150130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92577; 129962</t>
+          <t>105317; 150144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42333; 73075</t>
+          <t>41623; 71427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66814; 99537</t>
+          <t>65589; 100951</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45790; 70554</t>
+          <t>51888; 77676</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>141042; 192881</t>
+          <t>141766; 192641</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>181075; 236082</t>
+          <t>181790; 233932</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145712; 192446</t>
+          <t>166274; 217412</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111325</t>
+          <t>118338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>69674</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>173991</t>
+          <t>188013</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55295; 88763</t>
+          <t>56331; 90035</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63054; 100216</t>
+          <t>66304; 100298</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46837; 162806</t>
+          <t>98829; 140472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23499; 47311</t>
+          <t>23398; 47033</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45448; 76377</t>
+          <t>45959; 75650</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50063; 76348</t>
+          <t>57833; 83376</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>83737; 125676</t>
+          <t>85455; 126528</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120161; 168349</t>
+          <t>119106; 165816</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109820; 217133</t>
+          <t>164934; 212074</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47237</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>42235</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84879</t>
+          <t>97820</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12818; 33077</t>
+          <t>13841; 34144</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23727; 46407</t>
+          <t>23063; 47743</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35776; 60026</t>
+          <t>42080; 69434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10818; 30540</t>
+          <t>11411; 29424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15531; 36112</t>
+          <t>15679; 35636</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29462; 47965</t>
+          <t>32866; 53033</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29184; 55352</t>
+          <t>28289; 55477</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>43265; 75261</t>
+          <t>43972; 75397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69467; 102029</t>
+          <t>81797; 116318</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44902</t>
+          <t>51719</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6393; 24568</t>
+          <t>6377; 24775</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9632; 26611</t>
+          <t>8903; 25951</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19870; 35689</t>
+          <t>21488; 40629</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3656; 17114</t>
+          <t>3739; 16853</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11465; 28702</t>
+          <t>11153; 29155</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7327; 31933</t>
+          <t>15613; 29527</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13482; 36314</t>
+          <t>11829; 35185</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25209; 48354</t>
+          <t>23404; 49602</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20605; 60846</t>
+          <t>41422; 65203</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>20334</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3045; 18955</t>
+          <t>2189; 17132</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2412; 11279</t>
+          <t>2396; 12157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6925; 17641</t>
+          <t>8157; 20388</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2176; 12467</t>
+          <t>2141; 11716</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1362; 13194</t>
+          <t>1358; 12280</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3309; 13174</t>
+          <t>3557; 13634</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6777; 24470</t>
+          <t>6447; 24379</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6202; 19267</t>
+          <t>5333; 18607</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11705; 24770</t>
+          <t>13619; 29637</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>571302</t>
+          <t>617923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>289183</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>860485</t>
+          <t>940305</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>488666; 574007</t>
+          <t>491824; 580729</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>526414; 614737</t>
+          <t>527845; 612864</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>445002; 644667</t>
+          <t>559498; 671450</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>205139; 265688</t>
+          <t>204238; 268317</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>301638; 373426</t>
+          <t>303350; 371998</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>234173; 327856</t>
+          <t>291739; 358017</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>712616; 823438</t>
+          <t>713439; 818433</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>851221; 963781</t>
+          <t>847413; 967557</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>746871; 946601</t>
+          <t>875777; 1002298</t>
         </is>
       </c>
     </row>
